--- a/Sheet.xlsx
+++ b/Sheet.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="50">
   <si>
     <t>插件</t>
   </si>
@@ -37,6 +37,9 @@
     <t>文件夹</t>
   </si>
   <si>
+    <t>类型</t>
+  </si>
+  <si>
     <t>官网链接</t>
   </si>
   <si>
@@ -61,6 +64,12 @@
     <t>ParadoxNotion</t>
   </si>
   <si>
+    <t>可视化高级AI行为逻辑编辑工具</t>
+  </si>
+  <si>
+    <t>https://nodecanvas.paradoxnotion.com/</t>
+  </si>
+  <si>
     <t>FSM/Behaviour/DialogueTree</t>
   </si>
   <si>
@@ -70,6 +79,12 @@
     <t>vFolders</t>
   </si>
   <si>
+    <t>编辑器美化/增强</t>
+  </si>
+  <si>
+    <t>https://marketplace.unity.com/zh-CN/publishers/80066</t>
+  </si>
+  <si>
     <t>vFolders 2 keeps your project organized, speeds up development and just makes your life a bit better</t>
   </si>
   <si>
@@ -121,25 +136,49 @@
     <t>vFavorites Data不会被同步到Github</t>
   </si>
   <si>
-    <t>https://guavaman.com/projects/rewired/docs/</t>
-  </si>
-  <si>
-    <t>Rewired is a popular input system for Unity used by thousands of game studios, from indie to AAA. Add battle-tested cross-platform input to your game. Rewired is input that works.</t>
-  </si>
-  <si>
-    <t>游戏外设手柄键盘方向盘控制输入系統</t>
-  </si>
-  <si>
     <t>DOTween Pro</t>
   </si>
   <si>
+    <t>Demigiant</t>
+  </si>
+  <si>
+    <t>物体UI移动补间动画编辑插件</t>
+  </si>
+  <si>
     <t>http://dotween.demigiant.com/</t>
   </si>
   <si>
     <t>Animate gameObjects visually (move, shake, fade, rotate, change camera properties, and a lot more), draw paths in the editor and follow them, plus power-up DOTween's core with extra features</t>
   </si>
   <si>
-    <t>物体UI移动补间动画编辑插件</t>
+    <t>Odin Inspector</t>
+  </si>
+  <si>
+    <t>Tools/Sirenix</t>
+  </si>
+  <si>
+    <t>编辑器扩展/序列化</t>
+  </si>
+  <si>
+    <t>https://marketplace.unity.com/packages/tools/utilities/odin-inspector-and-serializer-89041</t>
+  </si>
+  <si>
+    <t>Odin is for anyone looking to improve and streamline their Unity workflow - create powerful custom tools and advanced, user-friendly editors and inspectors - without writing a single line of code.</t>
+  </si>
+  <si>
+    <t>PolygonPrototype</t>
+  </si>
+  <si>
+    <t>Prototype</t>
+  </si>
+  <si>
+    <t>原型3D模型</t>
+  </si>
+  <si>
+    <t>https://marketplace.unity.com/packages/essentials/tutorial-projects/polygon-prototype-pack-art-by-synty-137126</t>
+  </si>
+  <si>
+    <t>一个由道具、图标、角色、静态角色姿势和环境资源组成的低模原型资源包，用于为你的下一个游戏创建一个原型或灰盒。该资源包具有大量出色特征性资源，对于你的所有原型都是必不可少的。使用随附的注释和标记与你的团队沟通设计决策。使用 POLYGON 样式快速构建块和基元快速尝试想法。</t>
   </si>
 </sst>
 </file>
@@ -761,7 +800,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -769,6 +808,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
@@ -1085,18 +1127,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="13.2333333333333" customWidth="1"/>
-    <col min="2" max="2" width="13.0083333333333" customWidth="1"/>
-    <col min="3" max="3" width="14.65" customWidth="1"/>
-    <col min="4" max="4" width="36.1833333333333" customWidth="1"/>
-    <col min="5" max="5" width="10.1666666666667" customWidth="1"/>
-    <col min="6" max="6" width="24.5916666666667" customWidth="1"/>
+    <col min="1" max="1" width="11.975" customWidth="1"/>
+    <col min="2" max="2" width="9.94166666666667" customWidth="1"/>
+    <col min="3" max="4" width="14.65" customWidth="1"/>
+    <col min="5" max="5" width="36.1833333333333" customWidth="1"/>
+    <col min="6" max="6" width="10.1666666666667" customWidth="1"/>
+    <col min="7" max="7" width="24.5916666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1121,153 +1163,240 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
         <v>10</v>
       </c>
+      <c r="C2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" t="s">
-        <v>15</v>
+      <c r="G3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" t="s">
         <v>16</v>
       </c>
-      <c r="B4" t="s">
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G4" t="s">
-        <v>19</v>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H5" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>11</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="G5" t="s">
-        <v>23</v>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>22</v>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>31</v>
+      </c>
+      <c r="B7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="H7" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" t="s">
-        <v>11</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" t="s">
-        <v>29</v>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="C8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" t="s">
-        <v>11</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>32</v>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>42</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
-      <c r="A9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>36</v>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" t="s">
+        <v>49</v>
+      </c>
+      <c r="F10" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" display="https://guavaman.com/projects/rewired/docs/"/>
-    <hyperlink ref="C9" r:id="rId2" display="http://dotween.demigiant.com/"/>
+    <hyperlink ref="D8" r:id="rId1" display="http://dotween.demigiant.com/"/>
+    <hyperlink ref="D7" r:id="rId2" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
+    <hyperlink ref="D6" r:id="rId2" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
+    <hyperlink ref="D5" r:id="rId2" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
+    <hyperlink ref="D4" r:id="rId2" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
+    <hyperlink ref="D2" r:id="rId3" display="https://nodecanvas.paradoxnotion.com/"/>
+    <hyperlink ref="D9" r:id="rId4" display="https://marketplace.unity.com/packages/tools/utilities/odin-inspector-and-serializer-89041"/>
+    <hyperlink ref="D10" r:id="rId5" display="https://marketplace.unity.com/packages/essentials/tutorial-projects/polygon-prototype-pack-art-by-synty-137126"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Sheet.xlsx
+++ b/Sheet.xlsx
@@ -1,35 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17775"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+  <si>
+    <t/>
+  </si>
   <si>
     <t>插件</t>
   </si>
@@ -67,9 +56,6 @@
     <t>可视化高级AI行为逻辑编辑工具</t>
   </si>
   <si>
-    <t>https://nodecanvas.paradoxnotion.com/</t>
-  </si>
-  <si>
     <t>FSM/Behaviour/DialogueTree</t>
   </si>
   <si>
@@ -82,9 +68,6 @@
     <t>编辑器美化/增强</t>
   </si>
   <si>
-    <t>https://marketplace.unity.com/zh-CN/publishers/80066</t>
-  </si>
-  <si>
     <t>vFolders 2 keeps your project organized, speeds up development and just makes your life a bit better</t>
   </si>
   <si>
@@ -145,9 +128,6 @@
     <t>物体UI移动补间动画编辑插件</t>
   </si>
   <si>
-    <t>http://dotween.demigiant.com/</t>
-  </si>
-  <si>
     <t>Animate gameObjects visually (move, shake, fade, rotate, change camera properties, and a lot more), draw paths in the editor and follow them, plus power-up DOTween's core with extra features</t>
   </si>
   <si>
@@ -160,9 +140,6 @@
     <t>编辑器扩展/序列化</t>
   </si>
   <si>
-    <t>https://marketplace.unity.com/packages/tools/utilities/odin-inspector-and-serializer-89041</t>
-  </si>
-  <si>
     <t>Odin is for anyone looking to improve and streamline their Unity workflow - create powerful custom tools and advanced, user-friendly editors and inspectors - without writing a single line of code.</t>
   </si>
   <si>
@@ -175,182 +152,281 @@
     <t>原型3D模型</t>
   </si>
   <si>
-    <t>https://marketplace.unity.com/packages/essentials/tutorial-projects/polygon-prototype-pack-art-by-synty-137126</t>
-  </si>
-  <si>
     <t>一个由道具、图标、角色、静态角色姿势和环境资源组成的低模原型资源包，用于为你的下一个游戏创建一个原型或灰盒。该资源包具有大量出色特征性资源，对于你的所有原型都是必不可少的。使用随附的注释和标记与你的团队沟通设计决策。使用 POLYGON 样式快速构建块和基元快速尝试想法。</t>
+  </si>
+  <si>
+    <t>ALINE v1.7.8</t>
+  </si>
+  <si>
+    <t>辅助线绘制</t>
+  </si>
+  <si>
+    <t>https://arongranberg.com/aline/docs/drawingutilities2.html</t>
+  </si>
+  <si>
+    <t>提供很多 primitive（盒、球、圆柱、弧线、Bezier 等），并强调性能/渲染质量/统一 API。</t>
+  </si>
+  <si>
+    <t>2026.1.16</t>
+  </si>
+  <si>
+    <t>是UnityPackage，安装后放进Package路径下</t>
+  </si>
+  <si>
+    <t>是UnityPackage，安装后自动放进Packages路径下</t>
+  </si>
+  <si>
+    <r>
+      <t>https://nodecanvas.paradoxnotion.com/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>https://marketplace.unity.com/zh-CN/publishers/80066</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>https://marketplace.unity.com/zh-CN/publishers/80066</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>https://marketplace.unity.com/zh-CN/publishers/80066</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>https://marketplace.unity.com/zh-CN/publishers/80066</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>https://marketplace.unity.com/zh-CN/publishers/80066</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>http://dotween.demigiant.com/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>https://marketplace.unity.com/packages/tools/utilities/odin-inspector-and-serializer-89041</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>https://marketplace.unity.com/packages/essentials/tutorial-projects/polygon-prototype-pack-art-by-synty-137126</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
+    <numFmt numFmtId="300" formatCode="General"/>
+    <numFmt numFmtId="301" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="302" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="303" formatCode="0%"/>
+    <numFmt numFmtId="304" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="305" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
+  <fonts count="27">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF333333"/>
+      <color rgb="FF175CEB"/>
+      <sz val="10"/>
+      <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
       <name val="Arial Unicode MS"/>
       <charset val="134"/>
-    </font>
-    <font>
+      <color rgb="FF333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
       <u/>
-      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="FFECECEC"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <name val="Arial Unicode MS"/>
+      <color rgb="FF333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="true"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <i val="true"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="true"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="true"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="true"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="true"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="true"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="true"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="true"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -358,6 +434,9 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
@@ -407,19 +486,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -431,19 +510,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -455,19 +534,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -479,19 +558,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -503,19 +582,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -527,24 +606,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -581,7 +667,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.499985"/>
       </bottom>
       <diagonal/>
     </border>
@@ -651,180 +737,207 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+  <cellStyleXfs>
+    <xf numFmtId="300" fontId="8" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="9" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="301" fontId="8" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="302" fontId="8" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="303" fontId="8" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="304" fontId="8" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="305" fontId="8" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="4" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="8" fillId="3" borderId="2" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="10" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="11" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="12" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="13" fillId="2" borderId="3" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="14" fillId="2" borderId="3" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="15" fillId="2" borderId="4" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="15" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="16" fillId="4" borderId="5" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="17" fillId="5" borderId="6" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="18" fillId="5" borderId="5" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="19" fillId="6" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="20" fillId="2" borderId="8" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="21" fillId="2" borderId="9" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="22" fillId="7" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="8" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="9" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="25" fillId="10" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="26" fillId="11" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="26" fillId="12" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="25" fillId="13" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="25" fillId="14" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="26" fillId="15" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="26" fillId="16" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="25" fillId="17" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="25" fillId="18" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="26" fillId="19" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="26" fillId="20" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="25" fillId="21" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="25" fillId="22" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="26" fillId="23" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="26" fillId="24" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="25" fillId="25" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="25" fillId="26" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="26" fillId="27" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="26" fillId="28" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="25" fillId="29" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="25" fillId="30" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="26" fillId="31" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="26" fillId="32" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="25" fillId="33" borderId="1" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
+  <cellXfs count="14">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="8" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="9" fillId="2" borderId="1" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="5" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="8" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="3" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="2" builtinId="3"/>
+    <cellStyle name="货币" xfId="3" builtinId="4"/>
+    <cellStyle name="百分比" xfId="4" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="6" builtinId="7"/>
     <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
     <cellStyle name="注释" xfId="8" builtinId="10"/>
     <cellStyle name="警告文本" xfId="9" builtinId="11"/>
@@ -868,12 +981,6 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1006,7 +1113,7 @@
               <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="2700000" scaled="false"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -1019,7 +1126,7 @@
               <a:schemeClr val="phClr"/>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="2700000" scaled="0"/>
+          <a:lin ang="2700000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1049,7 +1156,7 @@
                 <a:schemeClr val="phClr"/>
               </a:gs>
             </a:gsLst>
-            <a:lin ang="2700000" scaled="1"/>
+            <a:lin ang="2700000" scaled="true"/>
           </a:gradFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
@@ -1058,7 +1165,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="101600" dist="50800" dir="5400000" algn="ctr" rotWithShape="false">
               <a:schemeClr val="phClr">
                 <a:alpha val="60000"/>
               </a:schemeClr>
@@ -1067,12 +1174,12 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="0"/>
+            <a:reflection stA="50000" endA="300" endPos="40000" dist="25400" dir="5400000" sy="-100000" algn="bl" rotWithShape="false"/>
           </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1090,7 +1197,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1115,7 +1222,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1125,278 +1232,298 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:I10"/>
+  <dimension ref="G11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="11.975" customWidth="1"/>
-    <col min="2" max="2" width="9.94166666666667" customWidth="1"/>
-    <col min="3" max="4" width="14.65" customWidth="1"/>
-    <col min="5" max="5" width="36.1833333333333" customWidth="1"/>
-    <col min="6" max="6" width="10.1666666666667" customWidth="1"/>
-    <col min="7" max="7" width="24.5916666666667" customWidth="1"/>
+    <col min="1" max="1" width="11.975" customWidth="true"/>
+    <col min="2" max="2" width="9.94167" customWidth="true"/>
+    <col min="3" max="4" width="14.65" customWidth="true"/>
+    <col min="5" max="5" width="36.1833" customWidth="true"/>
+    <col min="6" max="6" width="10.1667" customWidth="true"/>
+    <col min="7" max="7" width="24.5917" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+      <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="D1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="E1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="F1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="G1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="I1" s="4" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="D2" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>11</v>
+      <c r="G2" s="5" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
+    <row r="3" spans="1:8">
+      <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
+      <c r="G4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
+    <row r="5" spans="1:8">
+      <c r="A5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="D5" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" t="s">
-        <v>24</v>
+      <c r="G5" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s">
+    <row r="6" spans="1:7">
+      <c r="A6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="D6" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F5" t="s">
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H5" t="s">
-        <v>28</v>
+      <c r="G7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="s">
+    <row r="8" spans="1:7">
+      <c r="A8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>27</v>
+      <c r="G8" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" t="s">
+    <row r="9" spans="1:7">
+      <c r="A9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="H7" t="s">
-        <v>34</v>
+      <c r="G9" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F8" t="s">
+    <row r="10" spans="1:7">
+      <c r="A10" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="G8" s="3" t="s">
-        <v>37</v>
+      <c r="G10" s="5" t="s">
+        <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" t="s">
+    <row r="11" spans="1:7">
+      <c r="A11" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C11" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E11" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>47</v>
+      <c r="F11" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D8" r:id="rId1" display="http://dotween.demigiant.com/"/>
-    <hyperlink ref="D7" r:id="rId2" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
-    <hyperlink ref="D6" r:id="rId2" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
-    <hyperlink ref="D5" r:id="rId2" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
-    <hyperlink ref="D4" r:id="rId2" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
-    <hyperlink ref="D3" r:id="rId2" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
-    <hyperlink ref="D2" r:id="rId3" display="https://nodecanvas.paradoxnotion.com/"/>
-    <hyperlink ref="D9" r:id="rId4" display="https://marketplace.unity.com/packages/tools/utilities/odin-inspector-and-serializer-89041"/>
-    <hyperlink ref="D10" r:id="rId5" display="https://marketplace.unity.com/packages/essentials/tutorial-projects/polygon-prototype-pack-art-by-synty-137126"/>
+    <hyperlink ref="D2" r:id="rId0" display="https://nodecanvas.paradoxnotion.com/"/>
+    <hyperlink ref="D3" r:id="rId1" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
+    <hyperlink ref="D4" r:id="rId1" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
+    <hyperlink ref="D5" r:id="rId1" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
+    <hyperlink ref="D6" r:id="rId1" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
+    <hyperlink ref="D7" r:id="rId1" display="https://marketplace.unity.com/zh-CN/publishers/80066"/>
+    <hyperlink ref="D8" r:id="rId2" display="http://dotween.demigiant.com/"/>
+    <hyperlink ref="D9" r:id="rId3" display="https://marketplace.unity.com/packages/tools/utilities/odin-inspector-and-serializer-89041"/>
+    <hyperlink ref="D10" r:id="rId4" display="https://marketplace.unity.com/packages/essentials/tutorial-projects/polygon-prototype-pack-art-by-synty-137126"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -1405,7 +1532,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
@@ -1417,7 +1544,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>

--- a/Sheet.xlsx
+++ b/Sheet.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="75">
   <si>
     <t/>
   </si>
@@ -176,6 +176,15 @@
     <t>是UnityPackage，安装后自动放进Packages路径下</t>
   </si>
   <si>
+    <t>SRDebugger</t>
+  </si>
+  <si>
+    <t>StompyRobot</t>
+  </si>
+  <si>
+    <t>控制台/日志</t>
+  </si>
+  <si>
     <r>
       <t>https://nodecanvas.paradoxnotion.com/</t>
     </r>
@@ -218,6 +227,218 @@
   <si>
     <r>
       <t>https://marketplace.unity.com/packages/essentials/tutorial-projects/polygon-prototype-pack-art-by-synty-137126</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Inter"/>
+        <b val="true"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF212121"/>
+        <sz val="12"/>
+      </rPr>
+      <t>控制台</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Inter"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF212121"/>
+        <sz val="12"/>
+      </rPr>
+      <t>日志</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Inter"/>
+        <b val="true"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF212121"/>
+        <sz val="12"/>
+        <u val="none"/>
+      </rPr>
+      <t>控制台/</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Inter"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF212121"/>
+        <sz val="12"/>
+        <u val="none"/>
+      </rPr>
+      <t>日志</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Inter"/>
+        <b val="true"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF212121"/>
+        <sz val="12"/>
+      </rPr>
+      <t>SRDebugger</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+      </rPr>
+      <t>是一款可助你在目标设备上找出程序错误的工具。</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="微软雅黑"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF175CEB"/>
+        <sz val="11"/>
+        <u/>
+      </rPr>
+      <t>https://www.stompyrobot.uk/tools/srdebugger/documentation/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF175CEB"/>
+        <sz val="11"/>
+        <u/>
+      </rPr>
+      <t>https://www.stompyrobot.uk/tools/srdebugger/documentation/\n</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF175CEB"/>
+        <sz val="11"/>
+        <u/>
+      </rPr>
+      <t>https://www.stompyrobot.uk/tools/srdebugger/documentation/\n</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF175CEB"/>
+        <sz val="11"/>
+        <u/>
+      </rPr>
+      <t>https://marketplace.unity.com/packages/tools/gui/srdebugger-console-tools-on-device-27688</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="微软雅黑"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF175CEB"/>
+        <sz val="11"/>
+        <u/>
+      </rPr>
+      <t>https://arongranberg.com/aline/</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF175CEB"/>
+        <sz val="11"/>
+        <u/>
+      </rPr>
+      <t xml:space="preserve">https://arongranberg.com/aline/ </t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="宋体"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF175CEB"/>
+        <sz val="11"/>
+        <u/>
+      </rPr>
+      <t>https://marketplace.unity.com/packages/tools/gui/aline-162772</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF175CEB"/>
+        <sz val="11"/>
+        <u/>
+      </rPr>
+      <t>https://arongranberg.com/aline/ \n</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="宋体"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF175CEB"/>
+        <sz val="11"/>
+        <u/>
+      </rPr>
+      <t>https://marketplace.unity.com/packages/tools/gui/aline-162772</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="Inter"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF212121"/>
+        <sz val="12"/>
+        <u val="none"/>
+      </rPr>
+      <t>SRDebugger</t>
+    </r>
+    <r>
+      <rPr>
+        <rFont val="Arial Unicode MS"/>
+        <b val="false"/>
+        <i val="false"/>
+        <strike val="false"/>
+        <color rgb="FF333333"/>
+        <sz val="11"/>
+        <u val="none"/>
+      </rPr>
+      <t>是一款可助你在目标设备上找出程序错误的工具。</t>
     </r>
   </si>
 </sst>
@@ -233,7 +454,7 @@
     <numFmt numFmtId="304" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="305" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="37">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -424,6 +645,49 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Inter"/>
+      <color rgb="FF212121"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial Unicode MS"/>
+      <charset val="0"/>
+      <color rgb="FF333333"/>
+      <sz val="10"/>
+      <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial Unicode MS"/>
+      <color rgb="FF333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial Unicode MS"/>
+      <color rgb="FF333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+    </font>
+    <font>
+      <charset val="134"/>
+    </font>
+    <font/>
+    <font/>
+    <font>
+      <name val="Arial Unicode MS"/>
+      <b val="true"/>
+      <color rgb="FF333333"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u/>
     </font>
   </fonts>
   <fills count="34">
@@ -886,7 +1150,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -927,6 +1191,69 @@
       <alignment vertical="center"/>
     </xf>
     <xf fontId="3" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="27" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="7" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="30" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="32" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="33" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="34" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="35" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf fontId="29" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="36" fillId="2" borderId="1" xfId="1" applyFont="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="36" fillId="2" borderId="1" xfId="1" applyFont="true">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1234,7 +1561,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="G11"/>
+  <dimension ref="J13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="11.975" customWidth="true"/>
@@ -1274,244 +1601,314 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:11">
+      <c r="A2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="21" t="s">
         <v>12</v>
       </c>
       <c r="D2" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="25" t="s"/>
+      <c r="I2" s="25" t="s"/>
+      <c r="J2" s="25" t="s"/>
+      <c r="K2" s="25" t="s"/>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="25" t="s"/>
+      <c r="J3" s="25" t="s"/>
+      <c r="K3" s="25" t="s"/>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="25" t="s"/>
+      <c r="J4" s="25" t="s"/>
+      <c r="K4" s="25" t="s"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H5" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="25" t="s"/>
+      <c r="J5" s="25" t="s"/>
+      <c r="K5" s="25" t="s"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="25" t="s"/>
+      <c r="I6" s="25" t="s"/>
+      <c r="J6" s="25" t="s"/>
+      <c r="K6" s="25" t="s"/>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="I7" s="25" t="s"/>
+      <c r="J7" s="25" t="s"/>
+      <c r="K7" s="25" t="s"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="25" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="25" t="s">
+        <v>37</v>
+      </c>
+      <c r="F8" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" s="25" t="s"/>
+      <c r="I8" s="25" t="s"/>
+      <c r="J8" s="25" t="s"/>
+      <c r="K8" s="25" t="s"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="33" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H9" s="25" t="s"/>
+      <c r="I9" s="25" t="s"/>
+      <c r="J9" s="25" t="s"/>
+      <c r="K9" s="25" t="s"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="H10" s="25" t="s"/>
+      <c r="I10" s="25" t="s"/>
+      <c r="J10" s="25" t="s"/>
+      <c r="K10" s="25" t="s"/>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="B11" s="25" t="s"/>
+      <c r="C11" s="21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>73</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F11" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="H11" s="25" t="s"/>
+      <c r="I11" s="25" t="s"/>
+      <c r="J11" s="25" t="s"/>
+      <c r="K11" s="25" t="s"/>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>12</v>
-      </c>
+      <c r="B12" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="G12" s="25" t="s"/>
+      <c r="H12" s="25" t="s"/>
+      <c r="I12" s="25" t="s"/>
+      <c r="J12" s="25" t="s"/>
+      <c r="K12" s="25" t="s"/>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>52</v>
-      </c>
+    <row r="13" spans="5:10">
+      <c r="E13" s="27" t="s"/>
+      <c r="F13" s="27" t="s"/>
+      <c r="G13" s="27" t="s"/>
+      <c r="H13" s="27" t="s"/>
+      <c r="I13" s="27" t="s"/>
+      <c r="J13" s="27" t="s"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1524,6 +1921,8 @@
     <hyperlink ref="D8" r:id="rId2" display="http://dotween.demigiant.com/"/>
     <hyperlink ref="D9" r:id="rId3" display="https://marketplace.unity.com/packages/tools/utilities/odin-inspector-and-serializer-89041"/>
     <hyperlink ref="D10" r:id="rId4" display="https://marketplace.unity.com/packages/essentials/tutorial-projects/polygon-prototype-pack-art-by-synty-137126"/>
+    <hyperlink ref="D11" r:id="rId5"/>
+    <hyperlink ref="D12" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
